--- a/artfynd/A 5979-2023 artfynd.xlsx
+++ b/artfynd/A 5979-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5979-2023 artfynd.xlsx
+++ b/artfynd/A 5979-2023 artfynd.xlsx
@@ -675,62 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1673513</v>
+        <v>111401607</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>1440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Låssbytjärn, Vrm</t>
+          <t>Öst Låssbytjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318550.2266783514</v>
+        <v>318454</v>
       </c>
       <c r="R2" t="n">
-        <v>6596749.215144884</v>
+        <v>6596685</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,99 +765,78 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Örtrik granskog med tallinslag, torr mark nära väg</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Moss/örtmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johanna Bengtson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Bengtson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Roger Gran, Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1403311</v>
+        <v>111401477</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Låssbytjärn, Vrm</t>
+          <t>Öster Låssbytjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318550.2266783514</v>
+        <v>318590</v>
       </c>
       <c r="R3" t="n">
-        <v>6596749.215144884</v>
+        <v>6596681</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,84 +874,61 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Örtrik granskog med tallinslag, torr mark nära väg</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Moss/örtmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johanna Bengtson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Bengtson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Roger Gran, Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1749222</v>
+        <v>967488</v>
       </c>
       <c r="B4" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>1980</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Porslinsblå spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius cumatilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1004,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318431.0363940255</v>
+        <v>318504</v>
       </c>
       <c r="R4" t="n">
-        <v>6596677.598414334</v>
+        <v>6596716</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1037,19 +970,9 @@
           <t>2011-09-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,12 +1021,7 @@
         <v>1159412</v>
       </c>
       <c r="B5" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>318504.2588515503</v>
+        <v>318504</v>
       </c>
       <c r="R5" t="n">
-        <v>6596715.803344253</v>
+        <v>6596716</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1177,19 +1095,9 @@
           <t>2011-09-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,62 +1143,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>967488</v>
+        <v>111401715</v>
       </c>
       <c r="B6" t="n">
-        <v>85176</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1980</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Porslinsblå spindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius cumatilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Låssbytjärn, Vrm</t>
+          <t>Öst Låssbytjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>318504.2588515503</v>
+        <v>318647</v>
       </c>
       <c r="R6" t="n">
-        <v>6596715.803344253</v>
+        <v>6596736</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1314,22 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-09-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,101 +1225,76 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Örtrik granskog med tallinslag, västsluttning med rörligt markvatten</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Moss/örtmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johanna Bengtson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johanna Bengtson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Roger Gran, Jeanette Fahlstad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111401607</v>
+        <v>1403311</v>
       </c>
       <c r="B7" t="n">
-        <v>90685</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1440</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst Låssbytjärnet, Vrm</t>
+          <t>Låssbytjärn, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>318453.8345372439</v>
+        <v>318550</v>
       </c>
       <c r="R7" t="n">
-        <v>6596685.151500781</v>
+        <v>6596749</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1456,22 +1318,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1480,34 +1332,47 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Örtrik granskog med tallinslag, torr mark nära väg</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Moss/örtmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Johanna Bengtson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Gran, Jeanette Fahlstad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Johanna Bengtson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111401477</v>
+        <v>1295614</v>
       </c>
       <c r="B8" t="n">
-        <v>90651</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,48 +1380,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>4404</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster Låssbytjärnet, Vrm</t>
+          <t>Låssbytjärn, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>318589.7492944719</v>
+        <v>318431</v>
       </c>
       <c r="R8" t="n">
-        <v>6596680.635420629</v>
+        <v>6596678</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1580,22 +1443,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1604,34 +1457,47 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Glänta. Örtrik granskog med tallinslag, västsluttning med rörligt markvatten</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Vitmossa. Tjock förna på häll.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Johanna Bengtson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Gran, Jeanette Fahlstad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Johanna Bengtson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111401581</v>
+        <v>1749222</v>
       </c>
       <c r="B9" t="n">
-        <v>90710</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,48 +1505,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öst Låssbytjärnet, Vrm</t>
+          <t>Låssbytjärn, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>318450.5531044828</v>
+        <v>318431</v>
       </c>
       <c r="R9" t="n">
-        <v>6596617.106492633</v>
+        <v>6596678</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1704,22 +1568,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1728,22 +1582,40 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Örtrik granskog med tallinslag, västsluttning med rörligt markvatten</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Moss/örtmark</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Johanna Bengtson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Gran, Jeanette Fahlstad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Johanna Bengtson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
